--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ226"/>
+  <dimension ref="A1:AZ227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9239,10 +9239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130269983</v>
+        <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93235</v>
+        <v>93447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9250,24 +9250,28 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -9277,17 +9281,17 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>NV Buddby, Dannemora, Örbyhus, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>651969</v>
+        <v>651914</v>
       </c>
       <c r="R74" t="n">
-        <v>6673860</v>
+        <v>6674066</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9311,12 +9315,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9325,31 +9339,30 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Robert Petersen</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Robert Petersen</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130269983</t>
+          <t>https://artportalen.se/Sighting/136921484</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130685358</v>
+        <v>130269983</v>
       </c>
       <c r="B75" t="n">
         <v>93235</v>
@@ -9378,19 +9391,26 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Dannemora-Burunge/Tensta, Upl</t>
+          <t>NV Buddby, Dannemora, Örbyhus, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>652027</v>
+        <v>651969</v>
       </c>
       <c r="R75" t="n">
-        <v>6673853</v>
+        <v>6673860</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9428,34 +9448,31 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Robert Petersen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tilda Lindkvist</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering vid Sweco</t>
-        </is>
-      </c>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130685358</t>
+          <t>https://artportalen.se/Sighting/130269983</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130685359</v>
+        <v>130685358</v>
       </c>
       <c r="B76" t="n">
         <v>93235</v>
@@ -9483,26 +9500,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Dannemora-Burunge/Tensta, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>652026</v>
+        <v>652027</v>
       </c>
       <c r="R76" t="n">
-        <v>6673851</v>
+        <v>6673853</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9554,7 +9562,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Robert Petersen</t>
+          <t>Tilda Lindkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -9564,16 +9572,16 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130685359</t>
+          <t>https://artportalen.se/Sighting/130685358</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301031</v>
+        <v>130685359</v>
       </c>
       <c r="B77" t="n">
-        <v>75428</v>
+        <v>93235</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9581,40 +9589,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Dannemora-Burunge/Tensta, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651805</v>
+        <v>652026</v>
       </c>
       <c r="R77" t="n">
-        <v>6673899</v>
+        <v>6673851</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9638,22 +9652,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9668,74 +9672,69 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kirsi Jokinen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301031</t>
+          <t>https://artportalen.se/Sighting/130685359</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122260061</v>
+        <v>122301031</v>
       </c>
       <c r="B78" t="n">
-        <v>57950</v>
+        <v>75428</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>651886</v>
+        <v>651805</v>
       </c>
       <c r="R78" t="n">
-        <v>6674654</v>
+        <v>6673899</v>
       </c>
       <c r="S78" t="n">
         <v>4</v>
@@ -9762,22 +9761,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9803,13 +9802,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260061</t>
+          <t>https://artportalen.se/Sighting/122301031</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122260063</v>
+        <v>122260061</v>
       </c>
       <c r="B79" t="n">
         <v>57950</v>
@@ -9856,10 +9855,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>651872</v>
+        <v>651886</v>
       </c>
       <c r="R79" t="n">
-        <v>6674674</v>
+        <v>6674654</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -9891,7 +9890,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9901,7 +9900,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9927,13 +9926,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260063</t>
+          <t>https://artportalen.se/Sighting/122260061</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122260064</v>
+        <v>122260063</v>
       </c>
       <c r="B80" t="n">
         <v>57950</v>
@@ -9970,7 +9969,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -9980,10 +9979,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>651845</v>
+        <v>651872</v>
       </c>
       <c r="R80" t="n">
-        <v>6674626</v>
+        <v>6674674</v>
       </c>
       <c r="S80" t="n">
         <v>4</v>
@@ -10015,7 +10014,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10025,7 +10024,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10051,13 +10050,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260064</t>
+          <t>https://artportalen.se/Sighting/122260063</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122260066</v>
+        <v>122260064</v>
       </c>
       <c r="B81" t="n">
         <v>57950</v>
@@ -10094,7 +10093,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -10104,10 +10103,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>651934</v>
+        <v>651845</v>
       </c>
       <c r="R81" t="n">
-        <v>6674510</v>
+        <v>6674626</v>
       </c>
       <c r="S81" t="n">
         <v>4</v>
@@ -10139,7 +10138,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10149,7 +10148,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10175,13 +10174,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260066</t>
+          <t>https://artportalen.se/Sighting/122260064</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122260068</v>
+        <v>122260066</v>
       </c>
       <c r="B82" t="n">
         <v>57950</v>
@@ -10228,10 +10227,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>651928</v>
+        <v>651934</v>
       </c>
       <c r="R82" t="n">
-        <v>6674457</v>
+        <v>6674510</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -10263,7 +10262,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10273,7 +10272,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10299,13 +10298,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260068</t>
+          <t>https://artportalen.se/Sighting/122260066</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122260070</v>
+        <v>122260068</v>
       </c>
       <c r="B83" t="n">
         <v>57950</v>
@@ -10342,7 +10341,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -10352,10 +10351,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>651967</v>
+        <v>651928</v>
       </c>
       <c r="R83" t="n">
-        <v>6674433</v>
+        <v>6674457</v>
       </c>
       <c r="S83" t="n">
         <v>4</v>
@@ -10387,7 +10386,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10397,7 +10396,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10423,13 +10422,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260070</t>
+          <t>https://artportalen.se/Sighting/122260068</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122260071</v>
+        <v>122260070</v>
       </c>
       <c r="B84" t="n">
         <v>57950</v>
@@ -10466,7 +10465,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -10476,10 +10475,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>651930</v>
+        <v>651967</v>
       </c>
       <c r="R84" t="n">
-        <v>6674444</v>
+        <v>6674433</v>
       </c>
       <c r="S84" t="n">
         <v>4</v>
@@ -10511,7 +10510,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10521,7 +10520,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10547,13 +10546,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260071</t>
+          <t>https://artportalen.se/Sighting/122260070</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122260072</v>
+        <v>122260071</v>
       </c>
       <c r="B85" t="n">
         <v>57950</v>
@@ -10600,10 +10599,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>651927</v>
+        <v>651930</v>
       </c>
       <c r="R85" t="n">
-        <v>6674447</v>
+        <v>6674444</v>
       </c>
       <c r="S85" t="n">
         <v>4</v>
@@ -10635,7 +10634,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10645,7 +10644,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10671,13 +10670,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260072</t>
+          <t>https://artportalen.se/Sighting/122260071</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122260075</v>
+        <v>122260072</v>
       </c>
       <c r="B86" t="n">
         <v>57950</v>
@@ -10714,7 +10713,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -10724,10 +10723,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>651900</v>
+        <v>651927</v>
       </c>
       <c r="R86" t="n">
-        <v>6674390</v>
+        <v>6674447</v>
       </c>
       <c r="S86" t="n">
         <v>4</v>
@@ -10759,7 +10758,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10769,7 +10768,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10795,13 +10794,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260075</t>
+          <t>https://artportalen.se/Sighting/122260072</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122260076</v>
+        <v>122260075</v>
       </c>
       <c r="B87" t="n">
         <v>57950</v>
@@ -10848,10 +10847,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>651949</v>
+        <v>651900</v>
       </c>
       <c r="R87" t="n">
-        <v>6674279</v>
+        <v>6674390</v>
       </c>
       <c r="S87" t="n">
         <v>4</v>
@@ -10883,7 +10882,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10893,7 +10892,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10919,13 +10918,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260076</t>
+          <t>https://artportalen.se/Sighting/122260075</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122260077</v>
+        <v>122260076</v>
       </c>
       <c r="B88" t="n">
         <v>57950</v>
@@ -10972,10 +10971,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>651964</v>
+        <v>651949</v>
       </c>
       <c r="R88" t="n">
-        <v>6674220</v>
+        <v>6674279</v>
       </c>
       <c r="S88" t="n">
         <v>4</v>
@@ -11007,7 +11006,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11017,7 +11016,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11043,13 +11042,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260077</t>
+          <t>https://artportalen.se/Sighting/122260076</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122260080</v>
+        <v>122260077</v>
       </c>
       <c r="B89" t="n">
         <v>57950</v>
@@ -11086,7 +11085,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -11096,10 +11095,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>652019</v>
+        <v>651964</v>
       </c>
       <c r="R89" t="n">
-        <v>6674239</v>
+        <v>6674220</v>
       </c>
       <c r="S89" t="n">
         <v>4</v>
@@ -11131,7 +11130,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11141,7 +11140,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11167,13 +11166,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260080</t>
+          <t>https://artportalen.se/Sighting/122260077</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122260082</v>
+        <v>122260080</v>
       </c>
       <c r="B90" t="n">
         <v>57950</v>
@@ -11220,10 +11219,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>652114</v>
+        <v>652019</v>
       </c>
       <c r="R90" t="n">
-        <v>6674290</v>
+        <v>6674239</v>
       </c>
       <c r="S90" t="n">
         <v>4</v>
@@ -11255,7 +11254,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11265,7 +11264,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11291,13 +11290,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260082</t>
+          <t>https://artportalen.se/Sighting/122260080</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122300991</v>
+        <v>122260082</v>
       </c>
       <c r="B91" t="n">
         <v>57950</v>
@@ -11334,20 +11333,20 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651958</v>
+        <v>652114</v>
       </c>
       <c r="R91" t="n">
-        <v>6673868</v>
+        <v>6674290</v>
       </c>
       <c r="S91" t="n">
         <v>4</v>
@@ -11374,22 +11373,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11415,13 +11414,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122300991</t>
+          <t>https://artportalen.se/Sighting/122260082</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122300993</v>
+        <v>122300991</v>
       </c>
       <c r="B92" t="n">
         <v>57950</v>
@@ -11458,7 +11457,7 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -11468,13 +11467,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>651962</v>
+        <v>651958</v>
       </c>
       <c r="R92" t="n">
-        <v>6673882</v>
+        <v>6673868</v>
       </c>
       <c r="S92" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11503,7 +11502,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11513,12 +11512,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11544,13 +11538,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122300993</t>
+          <t>https://artportalen.se/Sighting/122300991</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122300994</v>
+        <v>122300993</v>
       </c>
       <c r="B93" t="n">
         <v>57950</v>
@@ -11587,7 +11581,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -11597,13 +11591,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>651915</v>
+        <v>651962</v>
       </c>
       <c r="R93" t="n">
-        <v>6673888</v>
+        <v>6673882</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11632,7 +11626,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11642,7 +11636,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11668,13 +11667,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122300994</t>
+          <t>https://artportalen.se/Sighting/122300993</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122300995</v>
+        <v>122300994</v>
       </c>
       <c r="B94" t="n">
         <v>57950</v>
@@ -11721,10 +11720,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>651899</v>
+        <v>651915</v>
       </c>
       <c r="R94" t="n">
-        <v>6673777</v>
+        <v>6673888</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -11756,7 +11755,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11766,7 +11765,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11792,13 +11791,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122300995</t>
+          <t>https://artportalen.se/Sighting/122300994</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122300997</v>
+        <v>122300995</v>
       </c>
       <c r="B95" t="n">
         <v>57950</v>
@@ -11835,20 +11834,20 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>651883</v>
+        <v>651899</v>
       </c>
       <c r="R95" t="n">
-        <v>6673732</v>
+        <v>6673777</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -11880,7 +11879,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11890,7 +11889,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11916,13 +11915,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122300997</t>
+          <t>https://artportalen.se/Sighting/122300995</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122300999</v>
+        <v>122300997</v>
       </c>
       <c r="B96" t="n">
         <v>57950</v>
@@ -11959,20 +11958,20 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>651879</v>
+        <v>651883</v>
       </c>
       <c r="R96" t="n">
-        <v>6673776</v>
+        <v>6673732</v>
       </c>
       <c r="S96" t="n">
         <v>4</v>
@@ -12004,7 +12003,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12014,7 +12013,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12040,13 +12039,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122300999</t>
+          <t>https://artportalen.se/Sighting/122300997</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122301001</v>
+        <v>122300999</v>
       </c>
       <c r="B97" t="n">
         <v>57950</v>
@@ -12093,10 +12092,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>651873</v>
+        <v>651879</v>
       </c>
       <c r="R97" t="n">
-        <v>6673779</v>
+        <v>6673776</v>
       </c>
       <c r="S97" t="n">
         <v>4</v>
@@ -12128,7 +12127,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12138,7 +12137,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12164,13 +12163,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301001</t>
+          <t>https://artportalen.se/Sighting/122300999</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122301004</v>
+        <v>122301001</v>
       </c>
       <c r="B98" t="n">
         <v>57950</v>
@@ -12217,10 +12216,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>651888</v>
+        <v>651873</v>
       </c>
       <c r="R98" t="n">
-        <v>6673877</v>
+        <v>6673779</v>
       </c>
       <c r="S98" t="n">
         <v>4</v>
@@ -12252,7 +12251,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12262,7 +12261,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12288,13 +12287,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301004</t>
+          <t>https://artportalen.se/Sighting/122301001</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122301006</v>
+        <v>122301004</v>
       </c>
       <c r="B99" t="n">
         <v>57950</v>
@@ -12341,10 +12340,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651860</v>
+        <v>651888</v>
       </c>
       <c r="R99" t="n">
-        <v>6673862</v>
+        <v>6673877</v>
       </c>
       <c r="S99" t="n">
         <v>4</v>
@@ -12376,7 +12375,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12386,7 +12385,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12412,13 +12411,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301006</t>
+          <t>https://artportalen.se/Sighting/122301004</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122301007</v>
+        <v>122301006</v>
       </c>
       <c r="B100" t="n">
         <v>57950</v>
@@ -12465,10 +12464,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>651778</v>
+        <v>651860</v>
       </c>
       <c r="R100" t="n">
-        <v>6673895</v>
+        <v>6673862</v>
       </c>
       <c r="S100" t="n">
         <v>4</v>
@@ -12500,7 +12499,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12510,7 +12509,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12536,13 +12535,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301007</t>
+          <t>https://artportalen.se/Sighting/122301006</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122301013</v>
+        <v>122301007</v>
       </c>
       <c r="B101" t="n">
         <v>57950</v>
@@ -12589,10 +12588,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>651745</v>
+        <v>651778</v>
       </c>
       <c r="R101" t="n">
-        <v>6673922</v>
+        <v>6673895</v>
       </c>
       <c r="S101" t="n">
         <v>4</v>
@@ -12624,7 +12623,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12634,7 +12633,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12660,13 +12659,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301013</t>
+          <t>https://artportalen.se/Sighting/122301007</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122301015</v>
+        <v>122301013</v>
       </c>
       <c r="B102" t="n">
         <v>57950</v>
@@ -12713,10 +12712,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>651777</v>
+        <v>651745</v>
       </c>
       <c r="R102" t="n">
-        <v>6673975</v>
+        <v>6673922</v>
       </c>
       <c r="S102" t="n">
         <v>4</v>
@@ -12748,7 +12747,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12758,7 +12757,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12784,13 +12783,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301015</t>
+          <t>https://artportalen.se/Sighting/122301013</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122301017</v>
+        <v>122301015</v>
       </c>
       <c r="B103" t="n">
         <v>57950</v>
@@ -12837,10 +12836,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>651776</v>
+        <v>651777</v>
       </c>
       <c r="R103" t="n">
-        <v>6673944</v>
+        <v>6673975</v>
       </c>
       <c r="S103" t="n">
         <v>4</v>
@@ -12872,7 +12871,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12882,7 +12881,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12908,13 +12907,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301017</t>
+          <t>https://artportalen.se/Sighting/122301015</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122301019</v>
+        <v>122301017</v>
       </c>
       <c r="B104" t="n">
         <v>57950</v>
@@ -12961,10 +12960,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>652004</v>
+        <v>651776</v>
       </c>
       <c r="R104" t="n">
-        <v>6673869</v>
+        <v>6673944</v>
       </c>
       <c r="S104" t="n">
         <v>4</v>
@@ -12996,7 +12995,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13006,7 +13005,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13032,13 +13031,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301019</t>
+          <t>https://artportalen.se/Sighting/122301017</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122301020</v>
+        <v>122301019</v>
       </c>
       <c r="B105" t="n">
         <v>57950</v>
@@ -13075,7 +13074,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -13085,10 +13084,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>652017</v>
+        <v>652004</v>
       </c>
       <c r="R105" t="n">
-        <v>6673872</v>
+        <v>6673869</v>
       </c>
       <c r="S105" t="n">
         <v>4</v>
@@ -13120,7 +13119,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13130,7 +13129,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13156,13 +13155,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301020</t>
+          <t>https://artportalen.se/Sighting/122301019</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122301021</v>
+        <v>122301020</v>
       </c>
       <c r="B106" t="n">
         <v>57950</v>
@@ -13205,11 +13204,11 @@
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>652056</v>
+        <v>652017</v>
       </c>
       <c r="R106" t="n">
         <v>6673872</v>
@@ -13244,7 +13243,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13254,7 +13253,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13280,13 +13279,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301021</t>
+          <t>https://artportalen.se/Sighting/122301020</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127786407</v>
+        <v>122301021</v>
       </c>
       <c r="B107" t="n">
         <v>57950</v>
@@ -13329,14 +13328,14 @@
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>651869</v>
+        <v>652056</v>
       </c>
       <c r="R107" t="n">
-        <v>6674698</v>
+        <v>6673872</v>
       </c>
       <c r="S107" t="n">
         <v>4</v>
@@ -13363,22 +13362,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13404,13 +13403,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786407</t>
+          <t>https://artportalen.se/Sighting/122301021</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127786410</v>
+        <v>127786407</v>
       </c>
       <c r="B108" t="n">
         <v>57950</v>
@@ -13457,10 +13456,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>651907</v>
+        <v>651869</v>
       </c>
       <c r="R108" t="n">
-        <v>6674624</v>
+        <v>6674698</v>
       </c>
       <c r="S108" t="n">
         <v>4</v>
@@ -13492,7 +13491,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13502,7 +13501,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13528,13 +13527,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786410</t>
+          <t>https://artportalen.se/Sighting/127786407</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127786413</v>
+        <v>127786410</v>
       </c>
       <c r="B109" t="n">
         <v>57950</v>
@@ -13571,7 +13570,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -13581,10 +13580,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>651946</v>
+        <v>651907</v>
       </c>
       <c r="R109" t="n">
-        <v>6674598</v>
+        <v>6674624</v>
       </c>
       <c r="S109" t="n">
         <v>4</v>
@@ -13616,7 +13615,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13626,7 +13625,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13652,13 +13651,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786413</t>
+          <t>https://artportalen.se/Sighting/127786410</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127786415</v>
+        <v>127786413</v>
       </c>
       <c r="B110" t="n">
         <v>57950</v>
@@ -13705,10 +13704,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>651859</v>
+        <v>651946</v>
       </c>
       <c r="R110" t="n">
-        <v>6674591</v>
+        <v>6674598</v>
       </c>
       <c r="S110" t="n">
         <v>4</v>
@@ -13740,7 +13739,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13750,7 +13749,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13776,13 +13775,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786415</t>
+          <t>https://artportalen.se/Sighting/127786413</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127786416</v>
+        <v>127786415</v>
       </c>
       <c r="B111" t="n">
         <v>57950</v>
@@ -13829,10 +13828,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>651903</v>
+        <v>651859</v>
       </c>
       <c r="R111" t="n">
-        <v>6674574</v>
+        <v>6674591</v>
       </c>
       <c r="S111" t="n">
         <v>4</v>
@@ -13864,7 +13863,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13874,7 +13873,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13900,13 +13899,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786416</t>
+          <t>https://artportalen.se/Sighting/127786415</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127786417</v>
+        <v>127786416</v>
       </c>
       <c r="B112" t="n">
         <v>57950</v>
@@ -13953,10 +13952,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>651998</v>
+        <v>651903</v>
       </c>
       <c r="R112" t="n">
-        <v>6674425</v>
+        <v>6674574</v>
       </c>
       <c r="S112" t="n">
         <v>4</v>
@@ -13988,7 +13987,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13998,7 +13997,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14024,13 +14023,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786417</t>
+          <t>https://artportalen.se/Sighting/127786416</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127786418</v>
+        <v>127786417</v>
       </c>
       <c r="B113" t="n">
         <v>57950</v>
@@ -14077,10 +14076,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>651997</v>
+        <v>651998</v>
       </c>
       <c r="R113" t="n">
-        <v>6674524</v>
+        <v>6674425</v>
       </c>
       <c r="S113" t="n">
         <v>4</v>
@@ -14112,7 +14111,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14122,7 +14121,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14148,13 +14147,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786418</t>
+          <t>https://artportalen.se/Sighting/127786417</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127786419</v>
+        <v>127786418</v>
       </c>
       <c r="B114" t="n">
         <v>57950</v>
@@ -14201,10 +14200,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>651988</v>
+        <v>651997</v>
       </c>
       <c r="R114" t="n">
-        <v>6674523</v>
+        <v>6674524</v>
       </c>
       <c r="S114" t="n">
         <v>4</v>
@@ -14236,7 +14235,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14246,7 +14245,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14272,13 +14271,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786419</t>
+          <t>https://artportalen.se/Sighting/127786418</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127786421</v>
+        <v>127786419</v>
       </c>
       <c r="B115" t="n">
         <v>57950</v>
@@ -14325,10 +14324,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>651978</v>
+        <v>651988</v>
       </c>
       <c r="R115" t="n">
-        <v>6674504</v>
+        <v>6674523</v>
       </c>
       <c r="S115" t="n">
         <v>4</v>
@@ -14360,7 +14359,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14370,7 +14369,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14396,13 +14395,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786421</t>
+          <t>https://artportalen.se/Sighting/127786419</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127786422</v>
+        <v>127786421</v>
       </c>
       <c r="B116" t="n">
         <v>57950</v>
@@ -14449,10 +14448,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>651823</v>
+        <v>651978</v>
       </c>
       <c r="R116" t="n">
-        <v>6674594</v>
+        <v>6674504</v>
       </c>
       <c r="S116" t="n">
         <v>4</v>
@@ -14484,7 +14483,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14494,7 +14493,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14520,13 +14519,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786422</t>
+          <t>https://artportalen.se/Sighting/127786421</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128089261</v>
+        <v>127786422</v>
       </c>
       <c r="B117" t="n">
         <v>57950</v>
@@ -14563,20 +14562,20 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>651870</v>
+        <v>651823</v>
       </c>
       <c r="R117" t="n">
-        <v>6673900</v>
+        <v>6674594</v>
       </c>
       <c r="S117" t="n">
         <v>4</v>
@@ -14603,22 +14602,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14644,13 +14643,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089261</t>
+          <t>https://artportalen.se/Sighting/127786422</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128089262</v>
+        <v>128089261</v>
       </c>
       <c r="B118" t="n">
         <v>57950</v>
@@ -14687,7 +14686,7 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
@@ -14697,10 +14696,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>651955</v>
+        <v>651870</v>
       </c>
       <c r="R118" t="n">
-        <v>6674002</v>
+        <v>6673900</v>
       </c>
       <c r="S118" t="n">
         <v>4</v>
@@ -14732,7 +14731,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14742,7 +14741,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14768,13 +14767,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089262</t>
+          <t>https://artportalen.se/Sighting/128089261</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128382450</v>
+        <v>128089262</v>
       </c>
       <c r="B119" t="n">
         <v>57950</v>
@@ -14811,20 +14810,20 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>651915</v>
+        <v>651955</v>
       </c>
       <c r="R119" t="n">
-        <v>6674236</v>
+        <v>6674002</v>
       </c>
       <c r="S119" t="n">
         <v>4</v>
@@ -14851,22 +14850,22 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14892,13 +14891,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128382450</t>
+          <t>https://artportalen.se/Sighting/128089262</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128453171</v>
+        <v>128382450</v>
       </c>
       <c r="B120" t="n">
         <v>57950</v>
@@ -14935,7 +14934,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -14945,13 +14944,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>651951</v>
+        <v>651915</v>
       </c>
       <c r="R120" t="n">
-        <v>6674438</v>
+        <v>6674236</v>
       </c>
       <c r="S120" t="n">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14975,27 +14974,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Lockande.</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15021,13 +15015,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128453171</t>
+          <t>https://artportalen.se/Sighting/128382450</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130684196</v>
+        <v>128453171</v>
       </c>
       <c r="B121" t="n">
         <v>57950</v>
@@ -15055,23 +15049,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Dannemora-Burunge/Tensta, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>652062</v>
+        <v>651951</v>
       </c>
       <c r="R121" t="n">
-        <v>6673877</v>
+        <v>6674438</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -15095,17 +15098,27 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Hackspår i talltorraka.</t>
+          <t>Lockande.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15120,48 +15133,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Robert Petersen</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering vid Sweco</t>
-        </is>
-      </c>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130684196</t>
+          <t>https://artportalen.se/Sighting/128453171</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130684203</v>
+        <v>130684196</v>
       </c>
       <c r="B122" t="n">
-        <v>58067</v>
+        <v>57950</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100090</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -15169,18 +15178,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -15188,10 +15188,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>652045</v>
+        <v>652062</v>
       </c>
       <c r="R122" t="n">
-        <v>6673978</v>
+        <v>6673877</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15226,6 +15226,11 @@
           <t>2025-10-22</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Hackspår i talltorraka.</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -15253,63 +15258,66 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130684203</t>
+          <t>https://artportalen.se/Sighting/130684196</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128089245</v>
+        <v>130684203</v>
       </c>
       <c r="B123" t="n">
-        <v>4775</v>
+        <v>58067</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100299</v>
+        <v>100090</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Dannemora-Burunge/Tensta, Upl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>651861</v>
+        <v>652045</v>
       </c>
       <c r="R123" t="n">
-        <v>6673883</v>
+        <v>6673978</v>
       </c>
       <c r="S123" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15333,29 +15341,19 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="b">
         <v>0</v>
@@ -15363,27 +15361,31 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kirsi Jokinen</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr"/>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089245</t>
+          <t>https://artportalen.se/Sighting/130684203</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128089247</v>
+        <v>128089245</v>
       </c>
       <c r="B124" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15391,21 +15393,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15414,7 +15416,7 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -15424,10 +15426,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>651986</v>
+        <v>651861</v>
       </c>
       <c r="R124" t="n">
-        <v>6673914</v>
+        <v>6673883</v>
       </c>
       <c r="S124" t="n">
         <v>4</v>
@@ -15459,7 +15461,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15469,14 +15471,14 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG124" t="b">
         <v>0</v>
@@ -15495,13 +15497,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089247</t>
+          <t>https://artportalen.se/Sighting/128089245</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128089248</v>
+        <v>128089247</v>
       </c>
       <c r="B125" t="n">
         <v>5179</v>
@@ -15535,20 +15537,20 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>651870</v>
+        <v>651986</v>
       </c>
       <c r="R125" t="n">
-        <v>6673697</v>
+        <v>6673914</v>
       </c>
       <c r="S125" t="n">
         <v>4</v>
@@ -15580,7 +15582,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15590,7 +15592,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15616,16 +15618,16 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089248</t>
+          <t>https://artportalen.se/Sighting/128089247</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122260085</v>
+        <v>128089248</v>
       </c>
       <c r="B126" t="n">
-        <v>58327</v>
+        <v>5179</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15633,49 +15635,46 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>651895</v>
+        <v>651870</v>
       </c>
       <c r="R126" t="n">
-        <v>6674630</v>
+        <v>6673697</v>
       </c>
       <c r="S126" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15699,22 +15698,22 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15740,13 +15739,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260085</t>
+          <t>https://artportalen.se/Sighting/128089248</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122301027</v>
+        <v>122260085</v>
       </c>
       <c r="B127" t="n">
         <v>58327</v>
@@ -15776,26 +15775,30 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>651983</v>
+        <v>651895</v>
       </c>
       <c r="R127" t="n">
-        <v>6673930</v>
+        <v>6674630</v>
       </c>
       <c r="S127" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15819,22 +15822,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15860,13 +15863,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301027</t>
+          <t>https://artportalen.se/Sighting/122260085</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127786430</v>
+        <v>122301027</v>
       </c>
       <c r="B128" t="n">
         <v>58327</v>
@@ -15894,24 +15897,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>651913</v>
+        <v>651983</v>
       </c>
       <c r="R128" t="n">
-        <v>6674473</v>
+        <v>6673930</v>
       </c>
       <c r="S128" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15935,22 +15942,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15973,20 +15980,16 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY128" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786430</t>
+          <t>https://artportalen.se/Sighting/122301027</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128089269</v>
+        <v>127786430</v>
       </c>
       <c r="B129" t="n">
         <v>58327</v>
@@ -16014,32 +16017,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>652058</v>
+        <v>651913</v>
       </c>
       <c r="R129" t="n">
-        <v>6673900</v>
+        <v>6674473</v>
       </c>
       <c r="S129" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -16063,22 +16058,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16101,16 +16096,20 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY129" t="inlineStr"/>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089269</t>
+          <t>https://artportalen.se/Sighting/127786430</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128382451</v>
+        <v>128089269</v>
       </c>
       <c r="B130" t="n">
         <v>58327</v>
@@ -16145,21 +16144,25 @@
       </c>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Bolsängen, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>652122</v>
+        <v>652058</v>
       </c>
       <c r="R130" t="n">
-        <v>6674192</v>
+        <v>6673900</v>
       </c>
       <c r="S130" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -16183,22 +16186,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16224,13 +16227,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128382451</t>
+          <t>https://artportalen.se/Sighting/128089269</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130684213</v>
+        <v>128382451</v>
       </c>
       <c r="B131" t="n">
         <v>58327</v>
@@ -16265,25 +16268,21 @@
       </c>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Dannemora-Burunge/Tensta, Upl</t>
+          <t>Bolsängen, Upl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>651886</v>
+        <v>652122</v>
       </c>
       <c r="R131" t="n">
-        <v>6673752</v>
+        <v>6674192</v>
       </c>
       <c r="S131" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16307,12 +16306,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16327,81 +16336,77 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Robert Petersen</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering vid Sweco</t>
-        </is>
-      </c>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130684213</t>
+          <t>https://artportalen.se/Sighting/128382451</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122260084</v>
+        <v>130684213</v>
       </c>
       <c r="B132" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Dannemora-Burunge/Tensta, Upl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>651900</v>
+        <v>651886</v>
       </c>
       <c r="R132" t="n">
-        <v>6674551</v>
+        <v>6673752</v>
       </c>
       <c r="S132" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16425,22 +16430,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16455,24 +16450,28 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kirsi Jokinen</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr"/>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260084</t>
+          <t>https://artportalen.se/Sighting/130684213</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122301025</v>
+        <v>122260084</v>
       </c>
       <c r="B133" t="n">
         <v>58114</v>
@@ -16519,13 +16518,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>651941</v>
+        <v>651900</v>
       </c>
       <c r="R133" t="n">
-        <v>6674093</v>
+        <v>6674551</v>
       </c>
       <c r="S133" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16549,22 +16548,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16590,13 +16589,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301025</t>
+          <t>https://artportalen.se/Sighting/122260084</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122301026</v>
+        <v>122301025</v>
       </c>
       <c r="B134" t="n">
         <v>58114</v>
@@ -16626,7 +16625,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -16639,14 +16638,14 @@
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>651977</v>
+        <v>651941</v>
       </c>
       <c r="R134" t="n">
-        <v>6673906</v>
+        <v>6674093</v>
       </c>
       <c r="S134" t="n">
         <v>45</v>
@@ -16678,7 +16677,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16688,7 +16687,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16714,13 +16713,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301026</t>
+          <t>https://artportalen.se/Sighting/122301025</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127786429</v>
+        <v>122301026</v>
       </c>
       <c r="B135" t="n">
         <v>58114</v>
@@ -16763,17 +16762,17 @@
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>652026</v>
+        <v>651977</v>
       </c>
       <c r="R135" t="n">
-        <v>6674488</v>
+        <v>6673906</v>
       </c>
       <c r="S135" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16797,22 +16796,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16835,20 +16834,16 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY135" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786429</t>
+          <t>https://artportalen.se/Sighting/122301026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128089267</v>
+        <v>127786429</v>
       </c>
       <c r="B136" t="n">
         <v>58114</v>
@@ -16891,17 +16886,17 @@
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Stubbolskärret, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>652012</v>
+        <v>652026</v>
       </c>
       <c r="R136" t="n">
-        <v>6674074</v>
+        <v>6674488</v>
       </c>
       <c r="S136" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16925,22 +16920,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16970,13 +16965,13 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089267</t>
+          <t>https://artportalen.se/Sighting/127786429</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128453172</v>
+        <v>128089267</v>
       </c>
       <c r="B137" t="n">
         <v>58114</v>
@@ -17019,17 +17014,17 @@
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Stubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>651958</v>
+        <v>652012</v>
       </c>
       <c r="R137" t="n">
-        <v>6674395</v>
+        <v>6674074</v>
       </c>
       <c r="S137" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -17053,22 +17048,22 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17091,16 +17086,20 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY137" t="inlineStr"/>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128453172</t>
+          <t>https://artportalen.se/Sighting/128089267</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130684181</v>
+        <v>128453172</v>
       </c>
       <c r="B138" t="n">
         <v>58114</v>
@@ -17130,30 +17129,30 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Dannemora-Burunge/Tensta, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>651877</v>
+        <v>651958</v>
       </c>
       <c r="R138" t="n">
-        <v>6673713</v>
+        <v>6674395</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -17177,12 +17176,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -17197,78 +17206,77 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Robert Petersen</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering vid Sweco</t>
-        </is>
-      </c>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130684181</t>
+          <t>https://artportalen.se/Sighting/128453172</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122260058</v>
+        <v>130684181</v>
       </c>
       <c r="B139" t="n">
-        <v>5199</v>
+        <v>58114</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Dannemora-Burunge/Tensta, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>652031</v>
+        <v>651877</v>
       </c>
       <c r="R139" t="n">
-        <v>6674226</v>
+        <v>6673713</v>
       </c>
       <c r="S139" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -17292,22 +17300,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17318,43 +17316,32 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kirsi Jokinen</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr"/>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260058</t>
+          <t>https://artportalen.se/Sighting/130684181</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122260059</v>
+        <v>122260058</v>
       </c>
       <c r="B140" t="n">
         <v>5199</v>
@@ -17398,10 +17385,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>652045</v>
+        <v>652031</v>
       </c>
       <c r="R140" t="n">
-        <v>6674236</v>
+        <v>6674226</v>
       </c>
       <c r="S140" t="n">
         <v>4</v>
@@ -17433,7 +17420,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17443,7 +17430,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17484,13 +17471,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260059</t>
+          <t>https://artportalen.se/Sighting/122260058</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>122300988</v>
+        <v>122260059</v>
       </c>
       <c r="B141" t="n">
         <v>5199</v>
@@ -17530,14 +17517,14 @@
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>651926</v>
+        <v>652045</v>
       </c>
       <c r="R141" t="n">
-        <v>6673844</v>
+        <v>6674236</v>
       </c>
       <c r="S141" t="n">
         <v>4</v>
@@ -17564,22 +17551,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17590,6 +17577,21 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
@@ -17605,13 +17607,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122300988</t>
+          <t>https://artportalen.se/Sighting/122260059</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127786403</v>
+        <v>122300988</v>
       </c>
       <c r="B142" t="n">
         <v>5199</v>
@@ -17651,14 +17653,14 @@
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>651940</v>
+        <v>651926</v>
       </c>
       <c r="R142" t="n">
-        <v>6674275</v>
+        <v>6673844</v>
       </c>
       <c r="S142" t="n">
         <v>4</v>
@@ -17685,22 +17687,22 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17726,13 +17728,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786403</t>
+          <t>https://artportalen.se/Sighting/122300988</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128089251</v>
+        <v>127786403</v>
       </c>
       <c r="B143" t="n">
         <v>5199</v>
@@ -17772,14 +17774,14 @@
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>652038</v>
+        <v>651940</v>
       </c>
       <c r="R143" t="n">
-        <v>6673850</v>
+        <v>6674275</v>
       </c>
       <c r="S143" t="n">
         <v>4</v>
@@ -17806,22 +17808,22 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17847,16 +17849,16 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089251</t>
+          <t>https://artportalen.se/Sighting/127786403</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130685519</v>
+        <v>128089251</v>
       </c>
       <c r="B144" t="n">
-        <v>8449</v>
+        <v>5199</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17864,37 +17866,46 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Dannemora-Burunge/Tensta, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>651942</v>
+        <v>652038</v>
       </c>
       <c r="R144" t="n">
-        <v>6673787</v>
+        <v>6673850</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -17918,12 +17929,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17938,81 +17959,65 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen, Tilda Lindkvist</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering vid Sweco</t>
-        </is>
-      </c>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130685519</t>
+          <t>https://artportalen.se/Sighting/128089251</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>122260110</v>
+        <v>130685519</v>
       </c>
       <c r="B145" t="n">
-        <v>99118</v>
+        <v>8449</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Dannemora-Burunge/Tensta, Upl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>651949</v>
+        <v>651942</v>
       </c>
       <c r="R145" t="n">
-        <v>6674420</v>
+        <v>6673787</v>
       </c>
       <c r="S145" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -18036,27 +18041,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18071,24 +18061,28 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kirsi Jokinen</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
-        </is>
-      </c>
-      <c r="AY145" t="inlineStr"/>
+          <t>Kirsi Jokinen, Tilda Lindkvist</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260110</t>
+          <t>https://artportalen.se/Sighting/130685519</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>122260111</v>
+        <v>122260110</v>
       </c>
       <c r="B146" t="n">
         <v>99118</v>
@@ -18118,7 +18112,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -18138,7 +18132,7 @@
         <v>651949</v>
       </c>
       <c r="R146" t="n">
-        <v>6674415</v>
+        <v>6674420</v>
       </c>
       <c r="S146" t="n">
         <v>4</v>
@@ -18170,7 +18164,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18180,7 +18174,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18206,13 +18205,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260111</t>
+          <t>https://artportalen.se/Sighting/122260110</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>122260113</v>
+        <v>122260111</v>
       </c>
       <c r="B147" t="n">
         <v>99118</v>
@@ -18242,7 +18241,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -18259,10 +18258,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>651906</v>
+        <v>651949</v>
       </c>
       <c r="R147" t="n">
-        <v>6674392</v>
+        <v>6674415</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -18294,7 +18293,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18304,7 +18303,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18330,13 +18329,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260113</t>
+          <t>https://artportalen.se/Sighting/122260111</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122260114</v>
+        <v>122260113</v>
       </c>
       <c r="B148" t="n">
         <v>99118</v>
@@ -18366,7 +18365,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -18383,10 +18382,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>652010</v>
+        <v>651906</v>
       </c>
       <c r="R148" t="n">
-        <v>6674220</v>
+        <v>6674392</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -18418,7 +18417,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18428,7 +18427,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18454,13 +18453,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260114</t>
+          <t>https://artportalen.se/Sighting/122260113</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122301050</v>
+        <v>122260114</v>
       </c>
       <c r="B149" t="n">
         <v>99118</v>
@@ -18490,7 +18489,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -18503,14 +18502,14 @@
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>651948</v>
+        <v>652010</v>
       </c>
       <c r="R149" t="n">
-        <v>6673906</v>
+        <v>6674220</v>
       </c>
       <c r="S149" t="n">
         <v>4</v>
@@ -18537,22 +18536,22 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18578,13 +18577,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301050</t>
+          <t>https://artportalen.se/Sighting/122260114</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>122301053</v>
+        <v>122301050</v>
       </c>
       <c r="B150" t="n">
         <v>99118</v>
@@ -18614,7 +18613,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -18631,10 +18630,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>651986</v>
+        <v>651948</v>
       </c>
       <c r="R150" t="n">
-        <v>6673841</v>
+        <v>6673906</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -18666,7 +18665,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18676,12 +18675,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18707,13 +18701,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301053</t>
+          <t>https://artportalen.se/Sighting/122301050</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>122301056</v>
+        <v>122301053</v>
       </c>
       <c r="B151" t="n">
         <v>99118</v>
@@ -18743,7 +18737,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -18760,10 +18754,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>651930</v>
+        <v>651986</v>
       </c>
       <c r="R151" t="n">
-        <v>6673898</v>
+        <v>6673841</v>
       </c>
       <c r="S151" t="n">
         <v>4</v>
@@ -18795,7 +18789,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18805,7 +18799,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18831,13 +18830,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301056</t>
+          <t>https://artportalen.se/Sighting/122301053</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>122301058</v>
+        <v>122301056</v>
       </c>
       <c r="B152" t="n">
         <v>99118</v>
@@ -18867,12 +18866,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -18884,10 +18883,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>651981</v>
+        <v>651930</v>
       </c>
       <c r="R152" t="n">
-        <v>6673859</v>
+        <v>6673898</v>
       </c>
       <c r="S152" t="n">
         <v>4</v>
@@ -18919,7 +18918,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18929,7 +18928,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18955,13 +18954,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301058</t>
+          <t>https://artportalen.se/Sighting/122301056</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122301060</v>
+        <v>122301058</v>
       </c>
       <c r="B153" t="n">
         <v>99118</v>
@@ -18991,12 +18990,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -19008,10 +19007,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>652000</v>
+        <v>651981</v>
       </c>
       <c r="R153" t="n">
-        <v>6673848</v>
+        <v>6673859</v>
       </c>
       <c r="S153" t="n">
         <v>4</v>
@@ -19043,7 +19042,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -19053,7 +19052,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -19079,13 +19078,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301060</t>
+          <t>https://artportalen.se/Sighting/122301058</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127786455</v>
+        <v>122301060</v>
       </c>
       <c r="B154" t="n">
         <v>99118</v>
@@ -19115,12 +19114,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -19128,14 +19127,14 @@
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>651872</v>
+        <v>652000</v>
       </c>
       <c r="R154" t="n">
-        <v>6674696</v>
+        <v>6673848</v>
       </c>
       <c r="S154" t="n">
         <v>4</v>
@@ -19162,22 +19161,22 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -19203,13 +19202,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786455</t>
+          <t>https://artportalen.se/Sighting/122301060</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127786457</v>
+        <v>127786455</v>
       </c>
       <c r="B155" t="n">
         <v>99118</v>
@@ -19239,7 +19238,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -19256,10 +19255,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>651935</v>
+        <v>651872</v>
       </c>
       <c r="R155" t="n">
-        <v>6674576</v>
+        <v>6674696</v>
       </c>
       <c r="S155" t="n">
         <v>4</v>
@@ -19291,7 +19290,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -19301,7 +19300,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -19327,13 +19326,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786457</t>
+          <t>https://artportalen.se/Sighting/127786455</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127786462</v>
+        <v>127786457</v>
       </c>
       <c r="B156" t="n">
         <v>99118</v>
@@ -19363,12 +19362,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -19380,10 +19379,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>651923</v>
+        <v>651935</v>
       </c>
       <c r="R156" t="n">
-        <v>6674461</v>
+        <v>6674576</v>
       </c>
       <c r="S156" t="n">
         <v>4</v>
@@ -19415,7 +19414,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -19425,7 +19424,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -19451,13 +19450,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786462</t>
+          <t>https://artportalen.se/Sighting/127786457</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127786463</v>
+        <v>127786462</v>
       </c>
       <c r="B157" t="n">
         <v>99118</v>
@@ -19487,7 +19486,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -19495,11 +19494,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
@@ -19508,10 +19503,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>651974</v>
+        <v>651923</v>
       </c>
       <c r="R157" t="n">
-        <v>6674401</v>
+        <v>6674461</v>
       </c>
       <c r="S157" t="n">
         <v>4</v>
@@ -19543,7 +19538,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -19553,7 +19548,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19579,13 +19574,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786463</t>
+          <t>https://artportalen.se/Sighting/127786462</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127786464</v>
+        <v>127786463</v>
       </c>
       <c r="B158" t="n">
         <v>99118</v>
@@ -19615,7 +19610,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -19623,7 +19618,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
@@ -19632,10 +19631,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>652028</v>
+        <v>651974</v>
       </c>
       <c r="R158" t="n">
-        <v>6674476</v>
+        <v>6674401</v>
       </c>
       <c r="S158" t="n">
         <v>4</v>
@@ -19667,7 +19666,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -19677,7 +19676,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19703,13 +19702,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786464</t>
+          <t>https://artportalen.se/Sighting/127786463</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127786465</v>
+        <v>127786464</v>
       </c>
       <c r="B159" t="n">
         <v>99118</v>
@@ -19739,12 +19738,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -19759,7 +19758,7 @@
         <v>652028</v>
       </c>
       <c r="R159" t="n">
-        <v>6674484</v>
+        <v>6674476</v>
       </c>
       <c r="S159" t="n">
         <v>4</v>
@@ -19791,7 +19790,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19801,7 +19800,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19827,13 +19826,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786465</t>
+          <t>https://artportalen.se/Sighting/127786464</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127786466</v>
+        <v>127786465</v>
       </c>
       <c r="B160" t="n">
         <v>99118</v>
@@ -19863,12 +19862,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -19880,10 +19879,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>651937</v>
+        <v>652028</v>
       </c>
       <c r="R160" t="n">
-        <v>6674398</v>
+        <v>6674484</v>
       </c>
       <c r="S160" t="n">
         <v>4</v>
@@ -19915,7 +19914,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19925,7 +19924,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19951,13 +19950,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786466</t>
+          <t>https://artportalen.se/Sighting/127786465</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128089315</v>
+        <v>127786466</v>
       </c>
       <c r="B161" t="n">
         <v>99118</v>
@@ -19987,7 +19986,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -20000,14 +19999,14 @@
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>651967</v>
+        <v>651937</v>
       </c>
       <c r="R161" t="n">
-        <v>6673901</v>
+        <v>6674398</v>
       </c>
       <c r="S161" t="n">
         <v>4</v>
@@ -20034,22 +20033,22 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -20075,13 +20074,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089315</t>
+          <t>https://artportalen.se/Sighting/127786466</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128089319</v>
+        <v>128089315</v>
       </c>
       <c r="B162" t="n">
         <v>99118</v>
@@ -20111,7 +20110,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -20128,10 +20127,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>651816</v>
+        <v>651967</v>
       </c>
       <c r="R162" t="n">
-        <v>6673882</v>
+        <v>6673901</v>
       </c>
       <c r="S162" t="n">
         <v>4</v>
@@ -20163,7 +20162,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -20173,7 +20172,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -20199,13 +20198,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089319</t>
+          <t>https://artportalen.se/Sighting/128089315</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128382563</v>
+        <v>128089319</v>
       </c>
       <c r="B163" t="n">
         <v>99118</v>
@@ -20235,7 +20234,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -20248,14 +20247,14 @@
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>651881</v>
+        <v>651816</v>
       </c>
       <c r="R163" t="n">
-        <v>6674706</v>
+        <v>6673882</v>
       </c>
       <c r="S163" t="n">
         <v>4</v>
@@ -20282,22 +20281,22 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -20323,13 +20322,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128382563</t>
+          <t>https://artportalen.se/Sighting/128089319</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128382564</v>
+        <v>128382563</v>
       </c>
       <c r="B164" t="n">
         <v>99118</v>
@@ -20359,7 +20358,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -20376,10 +20375,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>651972</v>
+        <v>651881</v>
       </c>
       <c r="R164" t="n">
-        <v>6674233</v>
+        <v>6674706</v>
       </c>
       <c r="S164" t="n">
         <v>4</v>
@@ -20411,7 +20410,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -20421,12 +20420,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>I mossan på grov rot till en tall.</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20452,13 +20446,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128382564</t>
+          <t>https://artportalen.se/Sighting/128382563</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128453206</v>
+        <v>128382564</v>
       </c>
       <c r="B165" t="n">
         <v>99118</v>
@@ -20488,7 +20482,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -20505,10 +20499,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>651917</v>
+        <v>651972</v>
       </c>
       <c r="R165" t="n">
-        <v>6674524</v>
+        <v>6674233</v>
       </c>
       <c r="S165" t="n">
         <v>4</v>
@@ -20535,22 +20529,27 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>I mossan på grov rot till en tall.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20576,48 +20575,48 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128453206</t>
+          <t>https://artportalen.se/Sighting/128382564</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127786486</v>
+        <v>128453206</v>
       </c>
       <c r="B166" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -20629,10 +20628,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>651896</v>
+        <v>651917</v>
       </c>
       <c r="R166" t="n">
-        <v>6674581</v>
+        <v>6674524</v>
       </c>
       <c r="S166" t="n">
         <v>4</v>
@@ -20659,22 +20658,22 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20700,13 +20699,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786486</t>
+          <t>https://artportalen.se/Sighting/128453206</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127786487</v>
+        <v>127786486</v>
       </c>
       <c r="B167" t="n">
         <v>106244</v>
@@ -20736,7 +20735,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -20753,10 +20752,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>651950</v>
+        <v>651896</v>
       </c>
       <c r="R167" t="n">
-        <v>6674353</v>
+        <v>6674581</v>
       </c>
       <c r="S167" t="n">
         <v>4</v>
@@ -20788,7 +20787,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -20798,7 +20797,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20824,43 +20823,43 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786487</t>
+          <t>https://artportalen.se/Sighting/127786486</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127786478</v>
+        <v>127786487</v>
       </c>
       <c r="B168" t="n">
-        <v>102241</v>
+        <v>106244</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -20877,10 +20876,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>651968</v>
+        <v>651950</v>
       </c>
       <c r="R168" t="n">
-        <v>6674476</v>
+        <v>6674353</v>
       </c>
       <c r="S168" t="n">
         <v>4</v>
@@ -20912,7 +20911,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -20922,12 +20921,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20953,13 +20947,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786478</t>
+          <t>https://artportalen.se/Sighting/127786487</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127786479</v>
+        <v>127786478</v>
       </c>
       <c r="B169" t="n">
         <v>102241</v>
@@ -20989,7 +20983,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -21006,10 +21000,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>651996</v>
+        <v>651968</v>
       </c>
       <c r="R169" t="n">
-        <v>6674470</v>
+        <v>6674476</v>
       </c>
       <c r="S169" t="n">
         <v>4</v>
@@ -21041,7 +21035,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -21051,7 +21045,12 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -21077,13 +21076,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786479</t>
+          <t>https://artportalen.se/Sighting/127786478</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127786481</v>
+        <v>127786479</v>
       </c>
       <c r="B170" t="n">
         <v>102241</v>
@@ -21113,7 +21112,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -21130,10 +21129,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>652011</v>
+        <v>651996</v>
       </c>
       <c r="R170" t="n">
-        <v>6674447</v>
+        <v>6674470</v>
       </c>
       <c r="S170" t="n">
         <v>4</v>
@@ -21165,7 +21164,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -21175,7 +21174,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -21201,13 +21200,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786481</t>
+          <t>https://artportalen.se/Sighting/127786479</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127786482</v>
+        <v>127786481</v>
       </c>
       <c r="B171" t="n">
         <v>102241</v>
@@ -21237,7 +21236,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -21254,10 +21253,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>652012</v>
+        <v>652011</v>
       </c>
       <c r="R171" t="n">
-        <v>6674454</v>
+        <v>6674447</v>
       </c>
       <c r="S171" t="n">
         <v>4</v>
@@ -21289,7 +21288,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -21299,7 +21298,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21325,13 +21324,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786482</t>
+          <t>https://artportalen.se/Sighting/127786481</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127786483</v>
+        <v>127786482</v>
       </c>
       <c r="B172" t="n">
         <v>102241</v>
@@ -21361,10 +21360,14 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
@@ -21374,10 +21377,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>651950</v>
+        <v>652012</v>
       </c>
       <c r="R172" t="n">
-        <v>6674474</v>
+        <v>6674454</v>
       </c>
       <c r="S172" t="n">
         <v>4</v>
@@ -21409,7 +21412,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -21419,7 +21422,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -21445,13 +21448,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786483</t>
+          <t>https://artportalen.se/Sighting/127786482</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128089325</v>
+        <v>127786483</v>
       </c>
       <c r="B173" t="n">
         <v>102241</v>
@@ -21481,27 +21484,23 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>652042</v>
+        <v>651950</v>
       </c>
       <c r="R173" t="n">
-        <v>6673900</v>
+        <v>6674474</v>
       </c>
       <c r="S173" t="n">
         <v>4</v>
@@ -21528,22 +21527,22 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -21569,13 +21568,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089325</t>
+          <t>https://artportalen.se/Sighting/127786483</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128089326</v>
+        <v>128089325</v>
       </c>
       <c r="B174" t="n">
         <v>102241</v>
@@ -21605,7 +21604,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -21622,10 +21621,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>651836</v>
+        <v>652042</v>
       </c>
       <c r="R174" t="n">
-        <v>6673959</v>
+        <v>6673900</v>
       </c>
       <c r="S174" t="n">
         <v>4</v>
@@ -21657,7 +21656,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -21667,7 +21666,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21693,13 +21692,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089326</t>
+          <t>https://artportalen.se/Sighting/128089325</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128089327</v>
+        <v>128089326</v>
       </c>
       <c r="B175" t="n">
         <v>102241</v>
@@ -21729,7 +21728,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -21742,14 +21741,14 @@
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>651905</v>
+        <v>651836</v>
       </c>
       <c r="R175" t="n">
-        <v>6674024</v>
+        <v>6673959</v>
       </c>
       <c r="S175" t="n">
         <v>4</v>
@@ -21781,7 +21780,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -21791,7 +21790,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -21817,13 +21816,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089327</t>
+          <t>https://artportalen.se/Sighting/128089326</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128089328</v>
+        <v>128089327</v>
       </c>
       <c r="B176" t="n">
         <v>102241</v>
@@ -21853,7 +21852,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -21870,10 +21869,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>651923</v>
+        <v>651905</v>
       </c>
       <c r="R176" t="n">
-        <v>6674022</v>
+        <v>6674024</v>
       </c>
       <c r="S176" t="n">
         <v>4</v>
@@ -21905,7 +21904,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -21915,7 +21914,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21941,13 +21940,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089328</t>
+          <t>https://artportalen.se/Sighting/128089327</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128382578</v>
+        <v>128089328</v>
       </c>
       <c r="B177" t="n">
         <v>102241</v>
@@ -21977,7 +21976,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -21994,10 +21993,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>651953</v>
+        <v>651923</v>
       </c>
       <c r="R177" t="n">
-        <v>6674461</v>
+        <v>6674022</v>
       </c>
       <c r="S177" t="n">
         <v>4</v>
@@ -22024,22 +22023,22 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -22065,13 +22064,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128382578</t>
+          <t>https://artportalen.se/Sighting/128089328</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128382579</v>
+        <v>128382578</v>
       </c>
       <c r="B178" t="n">
         <v>102241</v>
@@ -22101,7 +22100,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -22118,10 +22117,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>651968</v>
+        <v>651953</v>
       </c>
       <c r="R178" t="n">
-        <v>6674472</v>
+        <v>6674461</v>
       </c>
       <c r="S178" t="n">
         <v>4</v>
@@ -22153,7 +22152,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -22163,12 +22162,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -22194,42 +22188,50 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128382579</t>
+          <t>https://artportalen.se/Sighting/128382578</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122260115</v>
+        <v>128382579</v>
       </c>
       <c r="B179" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
@@ -22239,10 +22241,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>651891</v>
+        <v>651968</v>
       </c>
       <c r="R179" t="n">
-        <v>6674645</v>
+        <v>6674472</v>
       </c>
       <c r="S179" t="n">
         <v>4</v>
@@ -22269,22 +22271,27 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -22310,13 +22317,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260115</t>
+          <t>https://artportalen.se/Sighting/128382579</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122260116</v>
+        <v>122260115</v>
       </c>
       <c r="B180" t="n">
         <v>101326</v>
@@ -22355,10 +22362,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>651859</v>
+        <v>651891</v>
       </c>
       <c r="R180" t="n">
-        <v>6674654</v>
+        <v>6674645</v>
       </c>
       <c r="S180" t="n">
         <v>4</v>
@@ -22390,7 +22397,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -22400,7 +22407,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -22426,13 +22433,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260116</t>
+          <t>https://artportalen.se/Sighting/122260115</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>122260117</v>
+        <v>122260116</v>
       </c>
       <c r="B181" t="n">
         <v>101326</v>
@@ -22471,10 +22478,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>651906</v>
+        <v>651859</v>
       </c>
       <c r="R181" t="n">
-        <v>6674571</v>
+        <v>6674654</v>
       </c>
       <c r="S181" t="n">
         <v>4</v>
@@ -22506,7 +22513,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -22516,7 +22523,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -22542,13 +22549,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260117</t>
+          <t>https://artportalen.se/Sighting/122260116</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>122260118</v>
+        <v>122260117</v>
       </c>
       <c r="B182" t="n">
         <v>101326</v>
@@ -22587,10 +22594,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>651893</v>
+        <v>651906</v>
       </c>
       <c r="R182" t="n">
-        <v>6674508</v>
+        <v>6674571</v>
       </c>
       <c r="S182" t="n">
         <v>4</v>
@@ -22622,7 +22629,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -22632,7 +22639,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -22658,13 +22665,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260118</t>
+          <t>https://artportalen.se/Sighting/122260117</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>122260119</v>
+        <v>122260118</v>
       </c>
       <c r="B183" t="n">
         <v>101326</v>
@@ -22703,10 +22710,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>651950</v>
+        <v>651893</v>
       </c>
       <c r="R183" t="n">
-        <v>6674465</v>
+        <v>6674508</v>
       </c>
       <c r="S183" t="n">
         <v>4</v>
@@ -22738,7 +22745,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -22748,7 +22755,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22774,13 +22781,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260119</t>
+          <t>https://artportalen.se/Sighting/122260118</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>122260120</v>
+        <v>122260119</v>
       </c>
       <c r="B184" t="n">
         <v>101326</v>
@@ -22819,10 +22826,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>651967</v>
+        <v>651950</v>
       </c>
       <c r="R184" t="n">
-        <v>6674316</v>
+        <v>6674465</v>
       </c>
       <c r="S184" t="n">
         <v>4</v>
@@ -22854,7 +22861,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -22864,7 +22871,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -22890,13 +22897,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260120</t>
+          <t>https://artportalen.se/Sighting/122260119</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122260121</v>
+        <v>122260120</v>
       </c>
       <c r="B185" t="n">
         <v>101326</v>
@@ -22935,10 +22942,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>651955</v>
+        <v>651967</v>
       </c>
       <c r="R185" t="n">
-        <v>6674222</v>
+        <v>6674316</v>
       </c>
       <c r="S185" t="n">
         <v>4</v>
@@ -22970,7 +22977,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -22980,7 +22987,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -23006,13 +23013,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260121</t>
+          <t>https://artportalen.se/Sighting/122260120</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122260125</v>
+        <v>122260121</v>
       </c>
       <c r="B186" t="n">
         <v>101326</v>
@@ -23051,10 +23058,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>651973</v>
+        <v>651955</v>
       </c>
       <c r="R186" t="n">
-        <v>6674332</v>
+        <v>6674222</v>
       </c>
       <c r="S186" t="n">
         <v>4</v>
@@ -23086,7 +23093,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -23096,7 +23103,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -23122,13 +23129,13 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260125</t>
+          <t>https://artportalen.se/Sighting/122260121</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>122260126</v>
+        <v>122260125</v>
       </c>
       <c r="B187" t="n">
         <v>101326</v>
@@ -23167,10 +23174,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>651941</v>
+        <v>651973</v>
       </c>
       <c r="R187" t="n">
-        <v>6674469</v>
+        <v>6674332</v>
       </c>
       <c r="S187" t="n">
         <v>4</v>
@@ -23202,7 +23209,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -23212,7 +23219,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -23238,13 +23245,13 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122260126</t>
+          <t>https://artportalen.se/Sighting/122260125</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>122301062</v>
+        <v>122260126</v>
       </c>
       <c r="B188" t="n">
         <v>101326</v>
@@ -23272,29 +23279,21 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>651973</v>
+        <v>651941</v>
       </c>
       <c r="R188" t="n">
-        <v>6673897</v>
+        <v>6674469</v>
       </c>
       <c r="S188" t="n">
         <v>4</v>
@@ -23321,22 +23320,22 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -23362,13 +23361,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301062</t>
+          <t>https://artportalen.se/Sighting/122260126</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122301063</v>
+        <v>122301062</v>
       </c>
       <c r="B189" t="n">
         <v>101326</v>
@@ -23396,8 +23395,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
@@ -23407,10 +23414,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>651949</v>
+        <v>651973</v>
       </c>
       <c r="R189" t="n">
-        <v>6673910</v>
+        <v>6673897</v>
       </c>
       <c r="S189" t="n">
         <v>4</v>
@@ -23442,7 +23449,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -23452,7 +23459,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -23478,13 +23485,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301063</t>
+          <t>https://artportalen.se/Sighting/122301062</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122301064</v>
+        <v>122301063</v>
       </c>
       <c r="B190" t="n">
         <v>101326</v>
@@ -23523,10 +23530,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>651993</v>
+        <v>651949</v>
       </c>
       <c r="R190" t="n">
-        <v>6673896</v>
+        <v>6673910</v>
       </c>
       <c r="S190" t="n">
         <v>4</v>
@@ -23558,7 +23565,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -23568,7 +23575,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -23594,13 +23601,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301064</t>
+          <t>https://artportalen.se/Sighting/122301063</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122301065</v>
+        <v>122301064</v>
       </c>
       <c r="B191" t="n">
         <v>101326</v>
@@ -23639,10 +23646,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>652034</v>
+        <v>651993</v>
       </c>
       <c r="R191" t="n">
-        <v>6673906</v>
+        <v>6673896</v>
       </c>
       <c r="S191" t="n">
         <v>4</v>
@@ -23674,7 +23681,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -23684,7 +23691,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -23710,13 +23717,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301065</t>
+          <t>https://artportalen.se/Sighting/122301064</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122301066</v>
+        <v>122301065</v>
       </c>
       <c r="B192" t="n">
         <v>101326</v>
@@ -23755,10 +23762,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>652079</v>
+        <v>652034</v>
       </c>
       <c r="R192" t="n">
-        <v>6673929</v>
+        <v>6673906</v>
       </c>
       <c r="S192" t="n">
         <v>4</v>
@@ -23790,7 +23797,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -23800,7 +23807,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -23826,13 +23833,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301066</t>
+          <t>https://artportalen.se/Sighting/122301065</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122301067</v>
+        <v>122301066</v>
       </c>
       <c r="B193" t="n">
         <v>101326</v>
@@ -23871,10 +23878,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>652040</v>
+        <v>652079</v>
       </c>
       <c r="R193" t="n">
-        <v>6673920</v>
+        <v>6673929</v>
       </c>
       <c r="S193" t="n">
         <v>4</v>
@@ -23906,7 +23913,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -23916,7 +23923,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -23942,13 +23949,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301067</t>
+          <t>https://artportalen.se/Sighting/122301066</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122301068</v>
+        <v>122301067</v>
       </c>
       <c r="B194" t="n">
         <v>101326</v>
@@ -23983,14 +23990,14 @@
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>651906</v>
+        <v>652040</v>
       </c>
       <c r="R194" t="n">
-        <v>6673752</v>
+        <v>6673920</v>
       </c>
       <c r="S194" t="n">
         <v>4</v>
@@ -24022,7 +24029,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -24032,7 +24039,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -24058,13 +24065,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301068</t>
+          <t>https://artportalen.se/Sighting/122301067</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122301071</v>
+        <v>122301068</v>
       </c>
       <c r="B195" t="n">
         <v>101326</v>
@@ -24099,14 +24106,14 @@
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>651840</v>
+        <v>651906</v>
       </c>
       <c r="R195" t="n">
-        <v>6673881</v>
+        <v>6673752</v>
       </c>
       <c r="S195" t="n">
         <v>4</v>
@@ -24138,7 +24145,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -24148,7 +24155,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -24174,13 +24181,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301071</t>
+          <t>https://artportalen.se/Sighting/122301068</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122301073</v>
+        <v>122301071</v>
       </c>
       <c r="B196" t="n">
         <v>101326</v>
@@ -24219,10 +24226,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>651817</v>
+        <v>651840</v>
       </c>
       <c r="R196" t="n">
-        <v>6673939</v>
+        <v>6673881</v>
       </c>
       <c r="S196" t="n">
         <v>4</v>
@@ -24254,7 +24261,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -24264,7 +24271,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -24290,13 +24297,13 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301073</t>
+          <t>https://artportalen.se/Sighting/122301071</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122301074</v>
+        <v>122301073</v>
       </c>
       <c r="B197" t="n">
         <v>101326</v>
@@ -24335,10 +24342,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>651855</v>
+        <v>651817</v>
       </c>
       <c r="R197" t="n">
-        <v>6673907</v>
+        <v>6673939</v>
       </c>
       <c r="S197" t="n">
         <v>4</v>
@@ -24370,7 +24377,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -24380,7 +24387,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -24406,13 +24413,13 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301074</t>
+          <t>https://artportalen.se/Sighting/122301073</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122301075</v>
+        <v>122301074</v>
       </c>
       <c r="B198" t="n">
         <v>101326</v>
@@ -24451,10 +24458,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>651975</v>
+        <v>651855</v>
       </c>
       <c r="R198" t="n">
-        <v>6673928</v>
+        <v>6673907</v>
       </c>
       <c r="S198" t="n">
         <v>4</v>
@@ -24486,7 +24493,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -24496,7 +24503,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -24522,13 +24529,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301075</t>
+          <t>https://artportalen.se/Sighting/122301074</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122301077</v>
+        <v>122301075</v>
       </c>
       <c r="B199" t="n">
         <v>101326</v>
@@ -24567,10 +24574,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>651993</v>
+        <v>651975</v>
       </c>
       <c r="R199" t="n">
-        <v>6673867</v>
+        <v>6673928</v>
       </c>
       <c r="S199" t="n">
         <v>4</v>
@@ -24602,7 +24609,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -24612,7 +24619,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -24638,13 +24645,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301077</t>
+          <t>https://artportalen.se/Sighting/122301075</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122301078</v>
+        <v>122301077</v>
       </c>
       <c r="B200" t="n">
         <v>101326</v>
@@ -24683,10 +24690,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>652006</v>
+        <v>651993</v>
       </c>
       <c r="R200" t="n">
-        <v>6673876</v>
+        <v>6673867</v>
       </c>
       <c r="S200" t="n">
         <v>4</v>
@@ -24718,7 +24725,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -24728,7 +24735,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -24754,13 +24761,13 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301078</t>
+          <t>https://artportalen.se/Sighting/122301077</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122301079</v>
+        <v>122301078</v>
       </c>
       <c r="B201" t="n">
         <v>101326</v>
@@ -24799,10 +24806,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>652014</v>
+        <v>652006</v>
       </c>
       <c r="R201" t="n">
-        <v>6673954</v>
+        <v>6673876</v>
       </c>
       <c r="S201" t="n">
         <v>4</v>
@@ -24834,7 +24841,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -24844,7 +24851,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -24870,13 +24877,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301079</t>
+          <t>https://artportalen.se/Sighting/122301078</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122301080</v>
+        <v>122301079</v>
       </c>
       <c r="B202" t="n">
         <v>101326</v>
@@ -24915,10 +24922,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>652011</v>
+        <v>652014</v>
       </c>
       <c r="R202" t="n">
-        <v>6673969</v>
+        <v>6673954</v>
       </c>
       <c r="S202" t="n">
         <v>4</v>
@@ -24950,7 +24957,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -24960,7 +24967,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -24986,13 +24993,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301080</t>
+          <t>https://artportalen.se/Sighting/122301079</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122301081</v>
+        <v>122301080</v>
       </c>
       <c r="B203" t="n">
         <v>101326</v>
@@ -25031,10 +25038,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>652036</v>
+        <v>652011</v>
       </c>
       <c r="R203" t="n">
-        <v>6673988</v>
+        <v>6673969</v>
       </c>
       <c r="S203" t="n">
         <v>4</v>
@@ -25066,7 +25073,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -25076,7 +25083,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -25102,13 +25109,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301081</t>
+          <t>https://artportalen.se/Sighting/122301080</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127786468</v>
+        <v>122301081</v>
       </c>
       <c r="B204" t="n">
         <v>101326</v>
@@ -25143,14 +25150,14 @@
       <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>651849</v>
+        <v>652036</v>
       </c>
       <c r="R204" t="n">
-        <v>6674645</v>
+        <v>6673988</v>
       </c>
       <c r="S204" t="n">
         <v>4</v>
@@ -25177,22 +25184,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -25218,13 +25225,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786468</t>
+          <t>https://artportalen.se/Sighting/122301081</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127786470</v>
+        <v>127786468</v>
       </c>
       <c r="B205" t="n">
         <v>101326</v>
@@ -25263,10 +25270,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>651844</v>
+        <v>651849</v>
       </c>
       <c r="R205" t="n">
-        <v>6674682</v>
+        <v>6674645</v>
       </c>
       <c r="S205" t="n">
         <v>4</v>
@@ -25298,7 +25305,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -25308,7 +25315,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -25334,13 +25341,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786470</t>
+          <t>https://artportalen.se/Sighting/127786468</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127786471</v>
+        <v>127786470</v>
       </c>
       <c r="B206" t="n">
         <v>101326</v>
@@ -25379,10 +25386,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>651909</v>
+        <v>651844</v>
       </c>
       <c r="R206" t="n">
-        <v>6674658</v>
+        <v>6674682</v>
       </c>
       <c r="S206" t="n">
         <v>4</v>
@@ -25414,7 +25421,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -25424,7 +25431,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -25450,13 +25457,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786471</t>
+          <t>https://artportalen.se/Sighting/127786470</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127786472</v>
+        <v>127786471</v>
       </c>
       <c r="B207" t="n">
         <v>101326</v>
@@ -25495,10 +25502,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>651976</v>
+        <v>651909</v>
       </c>
       <c r="R207" t="n">
-        <v>6674481</v>
+        <v>6674658</v>
       </c>
       <c r="S207" t="n">
         <v>4</v>
@@ -25530,7 +25537,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -25540,7 +25547,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -25566,13 +25573,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786472</t>
+          <t>https://artportalen.se/Sighting/127786471</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127786473</v>
+        <v>127786472</v>
       </c>
       <c r="B208" t="n">
         <v>101326</v>
@@ -25611,10 +25618,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>652012</v>
+        <v>651976</v>
       </c>
       <c r="R208" t="n">
-        <v>6674422</v>
+        <v>6674481</v>
       </c>
       <c r="S208" t="n">
         <v>4</v>
@@ -25646,7 +25653,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -25656,7 +25663,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -25682,13 +25689,13 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786473</t>
+          <t>https://artportalen.se/Sighting/127786472</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127786474</v>
+        <v>127786473</v>
       </c>
       <c r="B209" t="n">
         <v>101326</v>
@@ -25727,10 +25734,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>652011</v>
+        <v>652012</v>
       </c>
       <c r="R209" t="n">
-        <v>6674446</v>
+        <v>6674422</v>
       </c>
       <c r="S209" t="n">
         <v>4</v>
@@ -25762,7 +25769,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -25772,7 +25779,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -25798,13 +25805,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786474</t>
+          <t>https://artportalen.se/Sighting/127786473</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127786475</v>
+        <v>127786474</v>
       </c>
       <c r="B210" t="n">
         <v>101326</v>
@@ -25832,16 +25839,8 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
@@ -25851,10 +25850,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>651955</v>
+        <v>652011</v>
       </c>
       <c r="R210" t="n">
-        <v>6674475</v>
+        <v>6674446</v>
       </c>
       <c r="S210" t="n">
         <v>4</v>
@@ -25886,7 +25885,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -25896,7 +25895,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -25922,13 +25921,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786475</t>
+          <t>https://artportalen.se/Sighting/127786474</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127786476</v>
+        <v>127786475</v>
       </c>
       <c r="B211" t="n">
         <v>101326</v>
@@ -25956,8 +25955,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
@@ -25967,10 +25974,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>651977</v>
+        <v>651955</v>
       </c>
       <c r="R211" t="n">
-        <v>6674348</v>
+        <v>6674475</v>
       </c>
       <c r="S211" t="n">
         <v>4</v>
@@ -26002,7 +26009,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -26012,7 +26019,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -26038,13 +26045,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786476</t>
+          <t>https://artportalen.se/Sighting/127786475</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127786477</v>
+        <v>127786476</v>
       </c>
       <c r="B212" t="n">
         <v>101326</v>
@@ -26083,10 +26090,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>651880</v>
+        <v>651977</v>
       </c>
       <c r="R212" t="n">
-        <v>6674598</v>
+        <v>6674348</v>
       </c>
       <c r="S212" t="n">
         <v>4</v>
@@ -26118,7 +26125,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -26128,7 +26135,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -26154,13 +26161,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127786477</t>
+          <t>https://artportalen.se/Sighting/127786476</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128089320</v>
+        <v>127786477</v>
       </c>
       <c r="B213" t="n">
         <v>101326</v>
@@ -26195,14 +26202,14 @@
       <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>651925</v>
+        <v>651880</v>
       </c>
       <c r="R213" t="n">
-        <v>6673733</v>
+        <v>6674598</v>
       </c>
       <c r="S213" t="n">
         <v>4</v>
@@ -26229,22 +26236,22 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -26270,13 +26277,13 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089320</t>
+          <t>https://artportalen.se/Sighting/127786477</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128089321</v>
+        <v>128089320</v>
       </c>
       <c r="B214" t="n">
         <v>101326</v>
@@ -26315,10 +26322,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>651896</v>
+        <v>651925</v>
       </c>
       <c r="R214" t="n">
-        <v>6673736</v>
+        <v>6673733</v>
       </c>
       <c r="S214" t="n">
         <v>4</v>
@@ -26350,7 +26357,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -26360,7 +26367,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -26386,13 +26393,13 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089321</t>
+          <t>https://artportalen.se/Sighting/128089320</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128089322</v>
+        <v>128089321</v>
       </c>
       <c r="B215" t="n">
         <v>101326</v>
@@ -26427,14 +26434,14 @@
       <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>651831</v>
+        <v>651896</v>
       </c>
       <c r="R215" t="n">
-        <v>6673992</v>
+        <v>6673736</v>
       </c>
       <c r="S215" t="n">
         <v>4</v>
@@ -26466,7 +26473,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -26476,7 +26483,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -26502,13 +26509,13 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089322</t>
+          <t>https://artportalen.se/Sighting/128089321</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128089323</v>
+        <v>128089322</v>
       </c>
       <c r="B216" t="n">
         <v>101326</v>
@@ -26547,10 +26554,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>651877</v>
+        <v>651831</v>
       </c>
       <c r="R216" t="n">
-        <v>6673919</v>
+        <v>6673992</v>
       </c>
       <c r="S216" t="n">
         <v>4</v>
@@ -26582,7 +26589,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -26592,7 +26599,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -26618,13 +26625,13 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128089323</t>
+          <t>https://artportalen.se/Sighting/128089322</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128382566</v>
+        <v>128089323</v>
       </c>
       <c r="B217" t="n">
         <v>101326</v>
@@ -26659,14 +26666,14 @@
       <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>651988</v>
+        <v>651877</v>
       </c>
       <c r="R217" t="n">
-        <v>6674237</v>
+        <v>6673919</v>
       </c>
       <c r="S217" t="n">
         <v>4</v>
@@ -26693,22 +26700,22 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -26734,13 +26741,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128382566</t>
+          <t>https://artportalen.se/Sighting/128089323</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128382567</v>
+        <v>128382566</v>
       </c>
       <c r="B218" t="n">
         <v>101326</v>
@@ -26775,14 +26782,14 @@
       <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Bolsängen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>652151</v>
+        <v>651988</v>
       </c>
       <c r="R218" t="n">
-        <v>6674184</v>
+        <v>6674237</v>
       </c>
       <c r="S218" t="n">
         <v>4</v>
@@ -26814,7 +26821,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -26824,7 +26831,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -26850,13 +26857,13 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128382567</t>
+          <t>https://artportalen.se/Sighting/128382566</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128382568</v>
+        <v>128382567</v>
       </c>
       <c r="B219" t="n">
         <v>101326</v>
@@ -26895,10 +26902,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>652156</v>
+        <v>652151</v>
       </c>
       <c r="R219" t="n">
-        <v>6674207</v>
+        <v>6674184</v>
       </c>
       <c r="S219" t="n">
         <v>4</v>
@@ -26930,7 +26937,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -26940,7 +26947,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -26966,13 +26973,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128382568</t>
+          <t>https://artportalen.se/Sighting/128382567</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128382569</v>
+        <v>128382568</v>
       </c>
       <c r="B220" t="n">
         <v>101326</v>
@@ -27011,10 +27018,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>652140</v>
+        <v>652156</v>
       </c>
       <c r="R220" t="n">
-        <v>6674239</v>
+        <v>6674207</v>
       </c>
       <c r="S220" t="n">
         <v>4</v>
@@ -27046,7 +27053,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -27056,7 +27063,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -27082,13 +27089,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128382569</t>
+          <t>https://artportalen.se/Sighting/128382568</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128382570</v>
+        <v>128382569</v>
       </c>
       <c r="B221" t="n">
         <v>101326</v>
@@ -27127,10 +27134,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>652129</v>
+        <v>652140</v>
       </c>
       <c r="R221" t="n">
-        <v>6674247</v>
+        <v>6674239</v>
       </c>
       <c r="S221" t="n">
         <v>4</v>
@@ -27162,7 +27169,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -27172,7 +27179,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -27198,13 +27205,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128382570</t>
+          <t>https://artportalen.se/Sighting/128382569</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128382574</v>
+        <v>128382570</v>
       </c>
       <c r="B222" t="n">
         <v>101326</v>
@@ -27239,14 +27246,14 @@
       <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Bolsängen, Upl</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>651947</v>
+        <v>652129</v>
       </c>
       <c r="R222" t="n">
-        <v>6674296</v>
+        <v>6674247</v>
       </c>
       <c r="S222" t="n">
         <v>4</v>
@@ -27278,7 +27285,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -27288,7 +27295,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -27314,16 +27321,16 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128382574</t>
+          <t>https://artportalen.se/Sighting/128382570</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>130684459</v>
+        <v>128382574</v>
       </c>
       <c r="B223" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -27349,21 +27356,23 @@
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Dannemora-Burunge/Tensta, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>652096</v>
+        <v>651947</v>
       </c>
       <c r="R223" t="n">
-        <v>6673984</v>
+        <v>6674296</v>
       </c>
       <c r="S223" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -27387,12 +27396,22 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -27401,35 +27420,30 @@
       <c r="AE223" t="b">
         <v>0</v>
       </c>
-      <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="b">
         <v>0</v>
       </c>
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Tilda Lindkvist</t>
-        </is>
-      </c>
-      <c r="AY223" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering vid Sweco</t>
-        </is>
-      </c>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130684459</t>
+          <t>https://artportalen.se/Sighting/128382574</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>130684476</v>
+        <v>130684459</v>
       </c>
       <c r="B224" t="n">
         <v>101325</v>
@@ -27458,8 +27472,6 @@
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
@@ -27468,10 +27480,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>651891</v>
+        <v>652096</v>
       </c>
       <c r="R224" t="n">
-        <v>6673718</v>
+        <v>6673984</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -27524,7 +27536,7 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Robert Petersen</t>
+          <t>Tilda Lindkvist</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -27534,57 +27546,58 @@
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130684476</t>
+          <t>https://artportalen.se/Sighting/130684459</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>122301037</v>
+        <v>130684476</v>
       </c>
       <c r="B225" t="n">
-        <v>92328</v>
+        <v>101325</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6040162</v>
+        <v>222498</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Dannemora-Burunge/Tensta, Upl</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>651917</v>
+        <v>651891</v>
       </c>
       <c r="R225" t="n">
-        <v>6673853</v>
+        <v>6673718</v>
       </c>
       <c r="S225" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -27608,22 +27621,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>11:54</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
-        </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>11:54</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -27632,33 +27635,38 @@
       <c r="AE225" t="b">
         <v>0</v>
       </c>
+      <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kirsi Jokinen</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
-        </is>
-      </c>
-      <c r="AY225" t="inlineStr"/>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122301037</t>
+          <t>https://artportalen.se/Sighting/130684476</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128089300</v>
+        <v>122301037</v>
       </c>
       <c r="B226" t="n">
-        <v>93211</v>
+        <v>92328</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -27666,19 +27674,23 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6047725</v>
+        <v>6040162</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr"/>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
@@ -27689,10 +27701,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>652032</v>
+        <v>651917</v>
       </c>
       <c r="R226" t="n">
-        <v>6673975</v>
+        <v>6673853</v>
       </c>
       <c r="S226" t="n">
         <v>4</v>
@@ -27719,27 +27731,22 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>På kalkrik mark med gran. Ingen tydlig mycelmatta. Ljusröda droppar på ung fruktkropp och brunröd saft i äldre, torrare fruktkropp. Korkaktig konsistens. Inga/få prickar i foten. Lite zonering i foten. Smakar papper med en aning pepparton.</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -27764,6 +27771,122 @@
       </c>
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122301037</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>128089300</v>
+      </c>
+      <c r="B227" t="n">
+        <v>93211</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Ackareåsen, Upl</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>652032</v>
+      </c>
+      <c r="R227" t="n">
+        <v>6673975</v>
+      </c>
+      <c r="S227" t="n">
+        <v>4</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>På kalkrik mark med gran. Ingen tydlig mycelmatta. Ljusröda droppar på ung fruktkropp och brunröd saft i äldre, torrare fruktkropp. Korkaktig konsistens. Inga/få prickar i foten. Lite zonering i foten. Smakar papper med en aning pepparton.</t>
+        </is>
+      </c>
+      <c r="AD227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT227" t="inlineStr"/>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128089300</t>
         </is>
@@ -27996,6 +28119,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -9242,7 +9242,7 @@
         <v>136921484</v>
       </c>
       <c r="B74" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
